--- a/Backtest/04-01-21/S&P500stock_04-01-21period252RS90.xlsx
+++ b/Backtest/04-01-21/S&P500stock_04-01-21period252RS90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="78">
   <si>
     <t>Stock</t>
   </si>
@@ -127,130 +127,127 @@
     <t>EM Rating</t>
   </si>
   <si>
-    <t>TSLA</t>
-  </si>
-  <si>
-    <t>POOL</t>
-  </si>
-  <si>
-    <t>AMD</t>
-  </si>
-  <si>
-    <t>CTLT</t>
-  </si>
-  <si>
-    <t>ALGN</t>
-  </si>
-  <si>
-    <t>TER</t>
-  </si>
-  <si>
-    <t>AMZN</t>
-  </si>
-  <si>
-    <t>NFLX</t>
-  </si>
-  <si>
-    <t>MPWR</t>
-  </si>
-  <si>
-    <t>QCOM</t>
-  </si>
-  <si>
-    <t>SNPS</t>
-  </si>
-  <si>
-    <t>PYPL</t>
+    <t>FCX</t>
+  </si>
+  <si>
+    <t>ON</t>
+  </si>
+  <si>
+    <t>GNRC</t>
+  </si>
+  <si>
+    <t>LEN</t>
+  </si>
+  <si>
+    <t>DHI</t>
+  </si>
+  <si>
+    <t>NWSA</t>
+  </si>
+  <si>
+    <t>PWR</t>
   </si>
   <si>
     <t>LRCX</t>
   </si>
   <si>
-    <t>FSLR</t>
-  </si>
-  <si>
-    <t>PTC</t>
-  </si>
-  <si>
-    <t>2021-01-27</t>
-  </si>
-  <si>
-    <t>2021-02-11</t>
-  </si>
-  <si>
-    <t>2021-01-26</t>
-  </si>
-  <si>
-    <t>2021-02-02</t>
-  </si>
-  <si>
-    <t>2021-02-03</t>
-  </si>
-  <si>
-    <t>2021-01-19</t>
-  </si>
-  <si>
-    <t>2021-02-04</t>
-  </si>
-  <si>
-    <t>2021-02-17</t>
-  </si>
-  <si>
-    <t>2021-02-25</t>
+    <t>AMAT</t>
+  </si>
+  <si>
+    <t>MOS</t>
+  </si>
+  <si>
+    <t>BLDR</t>
+  </si>
+  <si>
+    <t>DECK</t>
+  </si>
+  <si>
+    <t>EQT</t>
+  </si>
+  <si>
+    <t>TRGP</t>
+  </si>
+  <si>
+    <t>inf</t>
+  </si>
+  <si>
+    <t>2021-04-22</t>
+  </si>
+  <si>
+    <t>2021-05-03</t>
+  </si>
+  <si>
+    <t>2021-04-29</t>
+  </si>
+  <si>
+    <t>2021-06-16</t>
+  </si>
+  <si>
+    <t>2021-05-06</t>
+  </si>
+  <si>
+    <t>2021-04-21</t>
+  </si>
+  <si>
+    <t>2021-05-20</t>
+  </si>
+  <si>
+    <t>2021-05-05</t>
+  </si>
+  <si>
+    <t>Basic Materials</t>
+  </si>
+  <si>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>Industrials</t>
   </si>
   <si>
     <t>Consumer Cyclical</t>
   </si>
   <si>
-    <t>Industrials</t>
-  </si>
-  <si>
-    <t>Technology</t>
-  </si>
-  <si>
-    <t>Healthcare</t>
-  </si>
-  <si>
     <t>Communication Services</t>
   </si>
   <si>
-    <t>Financial Services</t>
-  </si>
-  <si>
-    <t>Auto Manufacturers</t>
-  </si>
-  <si>
-    <t>Industrial Distribution</t>
+    <t>Energy</t>
+  </si>
+  <si>
+    <t>Copper</t>
   </si>
   <si>
     <t>Semiconductors</t>
   </si>
   <si>
-    <t>Drug Manufacturers - Specialty &amp; Generic</t>
-  </si>
-  <si>
-    <t>Medical Instruments &amp; Supplies</t>
+    <t>Specialty Industrial Machinery</t>
+  </si>
+  <si>
+    <t>Residential Construction</t>
+  </si>
+  <si>
+    <t>Entertainment</t>
+  </si>
+  <si>
+    <t>Engineering &amp; Construction</t>
   </si>
   <si>
     <t>Semiconductor Equipment &amp; Materials</t>
   </si>
   <si>
-    <t>Internet Retail</t>
-  </si>
-  <si>
-    <t>Entertainment</t>
-  </si>
-  <si>
-    <t>Software - Infrastructure</t>
-  </si>
-  <si>
-    <t>Credit Services</t>
-  </si>
-  <si>
-    <t>Solar</t>
-  </si>
-  <si>
-    <t>Software - Application</t>
+    <t>Agricultural Inputs</t>
+  </si>
+  <si>
+    <t>Building Products &amp; Equipment</t>
+  </si>
+  <si>
+    <t>Footwear &amp; Accessories</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas E&amp;P</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas Midstream</t>
   </si>
 </sst>
 </file>
@@ -608,7 +605,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AK16"/>
+  <dimension ref="A1:AK15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:37">
@@ -729,43 +726,43 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>100</v>
+        <v>99.39393939393939</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="D2">
-        <v>235.22</v>
+        <v>32.93</v>
       </c>
       <c r="E2">
-        <v>3.84</v>
+        <v>4.23</v>
       </c>
       <c r="F2">
-        <v>2.661890954192657</v>
+        <v>1.098713937992248</v>
       </c>
       <c r="G2">
-        <v>3.54</v>
+        <v>4.05</v>
       </c>
       <c r="H2">
-        <v>1.023769748005721</v>
+        <v>1.315306824409996</v>
       </c>
       <c r="I2">
-        <v>226.1266662597656</v>
+        <v>32.35599975585937</v>
       </c>
       <c r="J2">
-        <v>215.0071655273437</v>
+        <v>34.22150001525879</v>
       </c>
       <c r="K2">
-        <v>177.9011325073242</v>
+        <v>32.88560009002686</v>
       </c>
       <c r="L2">
-        <v>110.8983630561829</v>
+        <v>21.75650001049042</v>
       </c>
       <c r="M2">
-        <v>1.05</v>
+        <v>0.95</v>
       </c>
       <c r="N2">
-        <v>1.27</v>
+        <v>0.98</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -774,64 +771,64 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>2.777777777777778</v>
+        <v>0</v>
       </c>
       <c r="U2" t="b">
         <v>0</v>
       </c>
       <c r="V2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W2" t="b">
         <v>1</v>
       </c>
       <c r="X2">
-        <v>23.37</v>
+        <v>6.14</v>
       </c>
       <c r="Y2">
-        <v>239.57</v>
+        <v>39.1</v>
       </c>
       <c r="Z2">
-        <v>474.06</v>
+        <v>38.02</v>
       </c>
       <c r="AA2">
-        <v>-14.64</v>
+        <v>-0.04</v>
       </c>
       <c r="AB2">
-        <v>173.82</v>
+        <v>180.39</v>
       </c>
       <c r="AC2">
-        <v>125.58</v>
+        <v>247.06</v>
       </c>
       <c r="AD2">
-        <v>2.18</v>
+        <v>4.6</v>
       </c>
       <c r="AE2">
-        <v>190.74</v>
+        <v>127.27</v>
       </c>
       <c r="AF2">
-        <v>447.76</v>
+        <v>633.33</v>
       </c>
       <c r="AG2">
-        <v>-85.84</v>
+        <v>108.82</v>
       </c>
       <c r="AH2" t="s">
         <v>52</v>
       </c>
       <c r="AI2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AJ2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AK2">
-        <v>59.48863157644212</v>
+        <v>70.35689183349629</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -839,49 +836,49 @@
         <v>38</v>
       </c>
       <c r="B3">
-        <v>95.15151515151516</v>
+        <v>97.97979797979798</v>
       </c>
       <c r="C3">
-        <v>482</v>
+        <v>104</v>
       </c>
       <c r="D3">
-        <v>372.5</v>
+        <v>41.61</v>
       </c>
       <c r="E3">
-        <v>1.57</v>
+        <v>4.26</v>
       </c>
       <c r="F3">
-        <v>-0.4001829306134235</v>
+        <v>1.13507799267757</v>
       </c>
       <c r="G3">
-        <v>2.87</v>
+        <v>3.54</v>
       </c>
       <c r="H3">
-        <v>0.2230782330284846</v>
+        <v>0.5320465469881975</v>
       </c>
       <c r="I3">
-        <v>366.2620056152344</v>
+        <v>39.88199920654297</v>
       </c>
       <c r="J3">
-        <v>351.3854995727539</v>
+        <v>39.12650012969971</v>
       </c>
       <c r="K3">
-        <v>350.0173999023438</v>
+        <v>38.9592000579834</v>
       </c>
       <c r="L3">
-        <v>291.757850189209</v>
+        <v>28.50490007400513</v>
       </c>
       <c r="M3">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="N3">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="P3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -890,10 +887,10 @@
         <v>0</v>
       </c>
       <c r="T3">
-        <v>2.777777777777778</v>
+        <v>0</v>
       </c>
       <c r="U3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" t="b">
         <v>1</v>
@@ -902,46 +899,46 @@
         <v>1</v>
       </c>
       <c r="X3">
-        <v>160.35</v>
+        <v>10.61</v>
       </c>
       <c r="Y3">
-        <v>391.5</v>
+        <v>42.38</v>
       </c>
       <c r="Z3">
-        <v>13.66</v>
+        <v>13.71</v>
       </c>
       <c r="AA3">
-        <v>18.81</v>
+        <v>33.89</v>
       </c>
       <c r="AB3">
-        <v>15.98</v>
+        <v>16.33</v>
       </c>
       <c r="AC3">
-        <v>560</v>
+        <v>800</v>
       </c>
       <c r="AD3">
-        <v>20.2</v>
+        <v>2.52</v>
       </c>
       <c r="AE3">
-        <v>-24.62</v>
-      </c>
-      <c r="AF3">
-        <v>411.69</v>
+        <v>-46.15</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>51</v>
       </c>
       <c r="AG3">
-        <v>71.11</v>
+        <v>100</v>
       </c>
       <c r="AH3" t="s">
         <v>53</v>
       </c>
       <c r="AI3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AJ3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AK3">
-        <v>53.62367651273764</v>
+        <v>45.85379349453701</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -949,43 +946,43 @@
         <v>39</v>
       </c>
       <c r="B4">
-        <v>96.76767676767678</v>
+        <v>98.18181818181819</v>
       </c>
       <c r="C4">
-        <v>10</v>
+        <v>413</v>
       </c>
       <c r="D4">
-        <v>91.70999999999999</v>
+        <v>327.45</v>
       </c>
       <c r="E4">
-        <v>1.73</v>
+        <v>3.44</v>
       </c>
       <c r="F4">
-        <v>-0.1843539343275324</v>
+        <v>0.141127164612085</v>
       </c>
       <c r="G4">
-        <v>2.42</v>
+        <v>3.85</v>
       </c>
       <c r="H4">
-        <v>-0.3146996501651817</v>
+        <v>1.008145931303409</v>
       </c>
       <c r="I4">
-        <v>91.60599975585939</v>
+        <v>313.0820068359375</v>
       </c>
       <c r="J4">
-        <v>93.19800033569337</v>
+        <v>313.2480026245117</v>
       </c>
       <c r="K4">
-        <v>86.91299987792969</v>
+        <v>304.5039999389649</v>
       </c>
       <c r="L4">
-        <v>70.07250003814697</v>
+        <v>217.7758993911743</v>
       </c>
       <c r="M4">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="N4">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -1006,52 +1003,52 @@
         <v>0</v>
       </c>
       <c r="V4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W4" t="b">
         <v>1</v>
       </c>
       <c r="X4">
-        <v>36.75</v>
+        <v>81.22</v>
       </c>
       <c r="Y4">
-        <v>97.98</v>
+        <v>364</v>
       </c>
       <c r="Z4">
-        <v>99.62</v>
+        <v>14.49</v>
       </c>
       <c r="AA4">
-        <v>-8.85</v>
+        <v>67.42</v>
       </c>
       <c r="AB4">
-        <v>116.97</v>
+        <v>17.36</v>
       </c>
       <c r="AC4">
-        <v>105.88</v>
+        <v>192.75</v>
       </c>
       <c r="AD4">
-        <v>10.09</v>
+        <v>8.99</v>
       </c>
       <c r="AE4">
-        <v>153.38</v>
+        <v>8.6</v>
       </c>
       <c r="AF4">
-        <v>-7.14</v>
+        <v>78.84999999999999</v>
       </c>
       <c r="AG4">
-        <v>-12.5</v>
+        <v>50.72</v>
       </c>
       <c r="AH4" t="s">
         <v>54</v>
       </c>
       <c r="AI4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AJ4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AK4">
-        <v>52.51618062292123</v>
+        <v>32.95725080153802</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1059,43 +1056,43 @@
         <v>40</v>
       </c>
       <c r="B5">
-        <v>96.36363636363636</v>
+        <v>93.73737373737374</v>
       </c>
       <c r="C5">
-        <v>371</v>
+        <v>215</v>
       </c>
       <c r="D5">
-        <v>104.07</v>
+        <v>98</v>
       </c>
       <c r="E5">
-        <v>1.67</v>
+        <v>4.27</v>
       </c>
       <c r="F5">
-        <v>-0.2652898079347417</v>
+        <v>1.147199344239344</v>
       </c>
       <c r="G5">
-        <v>2.18</v>
+        <v>3.24</v>
       </c>
       <c r="H5">
-        <v>-0.6015145212018033</v>
+        <v>0.07130520732831613</v>
       </c>
       <c r="I5">
-        <v>103.631999206543</v>
+        <v>97.70570983886719</v>
       </c>
       <c r="J5">
-        <v>99.87700004577637</v>
+        <v>90.72942848205567</v>
       </c>
       <c r="K5">
-        <v>98.43640045166016</v>
+        <v>86.53068725585938</v>
       </c>
       <c r="L5">
-        <v>81.53705024719238</v>
+        <v>75.5910456085205</v>
       </c>
       <c r="M5">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="N5">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -1113,7 +1110,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5" t="b">
         <v>1</v>
@@ -1122,46 +1119,46 @@
         <v>1</v>
       </c>
       <c r="X5">
-        <v>31.04</v>
+        <v>31.37</v>
       </c>
       <c r="Y5">
-        <v>120.48</v>
+        <v>101.19</v>
       </c>
       <c r="Z5">
-        <v>14.22</v>
+        <v>24.82</v>
       </c>
       <c r="AA5">
-        <v>6.16</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="AB5">
-        <v>35.83</v>
+        <v>23.4</v>
       </c>
       <c r="AC5">
-        <v>82.61</v>
+        <v>92.77</v>
       </c>
       <c r="AD5">
-        <v>2.67</v>
+        <v>5.35</v>
       </c>
       <c r="AE5">
-        <v>-53.33</v>
+        <v>13.48</v>
       </c>
       <c r="AF5">
-        <v>1025</v>
+        <v>32.39</v>
       </c>
       <c r="AG5">
-        <v>-65.22</v>
+        <v>28.31</v>
       </c>
       <c r="AH5" t="s">
         <v>55</v>
       </c>
       <c r="AI5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AJ5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AK5">
-        <v>39.86863496834323</v>
+        <v>30.25781573624338</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1169,46 +1166,46 @@
         <v>41</v>
       </c>
       <c r="B6">
-        <v>96.96969696969697</v>
+        <v>93.13131313131314</v>
       </c>
       <c r="C6">
-        <v>460</v>
+        <v>201</v>
       </c>
       <c r="D6">
-        <v>534.38</v>
+        <v>89.12</v>
       </c>
       <c r="E6">
-        <v>1.24</v>
+        <v>2.76</v>
       </c>
       <c r="F6">
-        <v>-0.8453302354530741</v>
+        <v>-0.6831247415885611</v>
       </c>
       <c r="G6">
-        <v>4.93</v>
+        <v>2.55</v>
       </c>
       <c r="H6">
-        <v>2.684905876092822</v>
+        <v>-0.9883998738894124</v>
       </c>
       <c r="I6">
-        <v>525.6080078125</v>
+        <v>88.42600097656251</v>
       </c>
       <c r="J6">
-        <v>520.2300033569336</v>
+        <v>83.70299987792968</v>
       </c>
       <c r="K6">
-        <v>483.8688031005859</v>
+        <v>80.47300003051758</v>
       </c>
       <c r="L6">
-        <v>319.9846501922607</v>
+        <v>72.11984983444214</v>
       </c>
       <c r="M6">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N6">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1220,10 +1217,10 @@
         <v>0</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="U6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" t="b">
         <v>1</v>
@@ -1232,46 +1229,46 @@
         <v>1</v>
       </c>
       <c r="X6">
-        <v>127.88</v>
+        <v>31.2</v>
       </c>
       <c r="Y6">
-        <v>543.65</v>
+        <v>91.05</v>
       </c>
       <c r="Z6">
-        <v>25.91</v>
+        <v>25.5</v>
       </c>
       <c r="AA6">
-        <v>83.59</v>
+        <v>21.82</v>
       </c>
       <c r="AB6">
-        <v>225.63</v>
+        <v>23.6</v>
       </c>
       <c r="AC6">
-        <v>14.94</v>
+        <v>64.39</v>
       </c>
       <c r="AD6">
-        <v>4.59</v>
+        <v>6.23</v>
       </c>
       <c r="AE6">
-        <v>440.38</v>
+        <v>-4.41</v>
       </c>
       <c r="AF6">
-        <v>-102.69</v>
+        <v>31.21</v>
       </c>
       <c r="AG6">
-        <v>1154.55</v>
+        <v>31.06</v>
       </c>
       <c r="AH6" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="AI6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AJ6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="AK6">
-        <v>39.55254286079886</v>
+        <v>29.38298416881012</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1279,43 +1276,43 @@
         <v>42</v>
       </c>
       <c r="B7">
-        <v>94.74747474747474</v>
+        <v>95.55555555555556</v>
       </c>
       <c r="C7">
-        <v>335</v>
+        <v>137</v>
       </c>
       <c r="D7">
-        <v>119.89</v>
+        <v>25.43</v>
       </c>
       <c r="E7">
-        <v>1.58</v>
+        <v>2.12</v>
       </c>
       <c r="F7">
-        <v>-0.3866936183455552</v>
+        <v>-1.45889124154211</v>
       </c>
       <c r="G7">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="H7">
-        <v>-0.7688231959731662</v>
+        <v>-1.710227972689893</v>
       </c>
       <c r="I7">
-        <v>118.7979995727539</v>
+        <v>25.61800003051758</v>
       </c>
       <c r="J7">
-        <v>117.8774997711182</v>
+        <v>25.71000003814697</v>
       </c>
       <c r="K7">
-        <v>107.1061999511719</v>
+        <v>23.24840007781982</v>
       </c>
       <c r="L7">
-        <v>83.27554990768432</v>
+        <v>17.11660002231598</v>
       </c>
       <c r="M7">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="N7">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1327,61 +1324,61 @@
         <v>0</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="U7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="b">
         <v>1</v>
       </c>
       <c r="X7">
-        <v>42.87</v>
+        <v>7.9</v>
       </c>
       <c r="Y7">
-        <v>122.37</v>
+        <v>27.68</v>
       </c>
       <c r="Z7">
-        <v>14.65</v>
+        <v>10.65</v>
       </c>
       <c r="AA7">
-        <v>404.54</v>
+        <v>138.94</v>
       </c>
       <c r="AB7">
-        <v>21.59</v>
+        <v>4.55</v>
       </c>
       <c r="AC7">
-        <v>81.08</v>
+        <v>131.45</v>
       </c>
       <c r="AD7">
-        <v>11.17</v>
+        <v>2.88</v>
       </c>
       <c r="AE7">
-        <v>17.54</v>
+        <v>550</v>
       </c>
       <c r="AF7">
-        <v>7.55</v>
+        <v>108.82</v>
       </c>
       <c r="AG7">
-        <v>43.24</v>
+        <v>45.16</v>
       </c>
       <c r="AH7" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="AI7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AJ7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AK7">
-        <v>35.38987516584783</v>
+        <v>20.98278603855748</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1389,43 +1386,43 @@
         <v>43</v>
       </c>
       <c r="B8">
-        <v>94.34343434343434</v>
+        <v>94.74747474747474</v>
       </c>
       <c r="C8">
-        <v>4</v>
+        <v>333</v>
       </c>
       <c r="D8">
-        <v>162.85</v>
+        <v>87.98</v>
       </c>
       <c r="E8">
-        <v>1.29</v>
+        <v>2.09</v>
       </c>
       <c r="F8">
-        <v>-0.777883674113733</v>
+        <v>-1.495255296227433</v>
       </c>
       <c r="G8">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="H8">
-        <v>-0.7449219567201144</v>
+        <v>-1.433783168893965</v>
       </c>
       <c r="I8">
-        <v>163.2143005371094</v>
+        <v>86.09800109863281</v>
       </c>
       <c r="J8">
-        <v>159.8172256469726</v>
+        <v>85.42900047302246</v>
       </c>
       <c r="K8">
-        <v>158.6557104492188</v>
+        <v>80.66840011596679</v>
       </c>
       <c r="L8">
-        <v>143.8660596084595</v>
+        <v>62.40645013809204</v>
       </c>
       <c r="M8">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1443,55 +1440,55 @@
         <v>0</v>
       </c>
       <c r="U8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="b">
         <v>1</v>
       </c>
       <c r="W8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X8">
-        <v>81.3</v>
+        <v>28.71</v>
       </c>
       <c r="Y8">
-        <v>177.61</v>
+        <v>88.97</v>
       </c>
       <c r="Z8">
-        <v>1612.15</v>
+        <v>10.46</v>
       </c>
       <c r="AA8">
-        <v>4546.61</v>
+        <v>21.3</v>
       </c>
       <c r="AB8">
-        <v>17.36</v>
+        <v>3.96</v>
       </c>
       <c r="AC8">
-        <v>91.65000000000001</v>
+        <v>340.74</v>
       </c>
       <c r="AD8">
-        <v>7.65</v>
+        <v>3.95</v>
       </c>
       <c r="AE8">
-        <v>20.29</v>
+        <v>2.59</v>
       </c>
       <c r="AF8">
-        <v>106.29</v>
+        <v>118.87</v>
       </c>
       <c r="AG8">
-        <v>-22.76</v>
+        <v>96.3</v>
       </c>
       <c r="AH8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AI8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AJ8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AK8">
-        <v>34.75778334417058</v>
+        <v>18.46720555734559</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1499,43 +1496,43 @@
         <v>44</v>
       </c>
       <c r="B9">
-        <v>92.32323232323232</v>
+        <v>90.90909090909091</v>
       </c>
       <c r="C9">
-        <v>114</v>
+        <v>30</v>
       </c>
       <c r="D9">
-        <v>540.73</v>
+        <v>59.52</v>
       </c>
       <c r="E9">
-        <v>1.92</v>
+        <v>3.96</v>
       </c>
       <c r="F9">
-        <v>0.07194299876196328</v>
+        <v>0.7714374458243436</v>
       </c>
       <c r="G9">
-        <v>2.4</v>
+        <v>3.81</v>
       </c>
       <c r="H9">
-        <v>-0.3386008894182335</v>
+        <v>0.9467137526820911</v>
       </c>
       <c r="I9">
-        <v>525.8559936523437</v>
+        <v>57.40699996948242</v>
       </c>
       <c r="J9">
-        <v>517.8279998779296</v>
+        <v>54.73599987030029</v>
       </c>
       <c r="K9">
-        <v>500.3863989257812</v>
+        <v>54.97467987060547</v>
       </c>
       <c r="L9">
-        <v>471.5225495910644</v>
+        <v>42.82058986663819</v>
       </c>
       <c r="M9">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N9">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -1553,55 +1550,55 @@
         <v>0</v>
       </c>
       <c r="U9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" t="b">
         <v>1</v>
       </c>
       <c r="W9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9">
-        <v>290.25</v>
+        <v>21.33</v>
       </c>
       <c r="Y9">
-        <v>575.37</v>
+        <v>60.36</v>
       </c>
       <c r="Z9">
-        <v>227.56</v>
+        <v>68.91</v>
       </c>
       <c r="AA9">
-        <v>545.47</v>
+        <v>104.47</v>
       </c>
       <c r="AB9">
-        <v>39.17</v>
+        <v>13.6</v>
       </c>
       <c r="AC9">
-        <v>34.59</v>
+        <v>52.53</v>
       </c>
       <c r="AD9">
-        <v>7.64</v>
+        <v>15.78</v>
       </c>
       <c r="AE9">
-        <v>9.82</v>
+        <v>6.53</v>
       </c>
       <c r="AF9">
-        <v>1.24</v>
+        <v>18.12</v>
       </c>
       <c r="AG9">
-        <v>21.05</v>
+        <v>21.21</v>
       </c>
       <c r="AH9" t="s">
         <v>57</v>
       </c>
       <c r="AI9" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="AJ9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AK9">
-        <v>32.23684864305017</v>
+        <v>16.96763499234857</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1609,58 +1606,58 @@
         <v>45</v>
       </c>
       <c r="B10">
-        <v>98.18181818181819</v>
+        <v>95.75757575757575</v>
       </c>
       <c r="C10">
-        <v>461</v>
+        <v>42</v>
       </c>
       <c r="D10">
-        <v>366.23</v>
+        <v>133.6</v>
       </c>
       <c r="E10">
-        <v>2.03</v>
+        <v>4.28</v>
       </c>
       <c r="F10">
-        <v>0.2203254337085133</v>
+        <v>1.159320695801118</v>
       </c>
       <c r="G10">
-        <v>2.94</v>
+        <v>3.86</v>
       </c>
       <c r="H10">
-        <v>0.3067325704141658</v>
+        <v>1.023503975958738</v>
       </c>
       <c r="I10">
-        <v>359.3360046386719</v>
+        <v>126.8860015869141</v>
       </c>
       <c r="J10">
-        <v>336.8925018310547</v>
+        <v>117.9705001831055</v>
       </c>
       <c r="K10">
-        <v>325.2182019042968</v>
+        <v>113.1163999938965</v>
       </c>
       <c r="L10">
-        <v>256.6587506866455</v>
+        <v>80.35760023117065</v>
       </c>
       <c r="M10">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N10">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="P10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10">
         <v>0</v>
       </c>
       <c r="R10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>7.777777777777777</v>
+        <v>0</v>
       </c>
       <c r="U10" t="b">
         <v>0</v>
@@ -1669,49 +1666,49 @@
         <v>1</v>
       </c>
       <c r="W10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X10">
-        <v>130.12</v>
+        <v>41.58</v>
       </c>
       <c r="Y10">
-        <v>367.05</v>
+        <v>135.5</v>
       </c>
       <c r="Z10">
-        <v>13.13</v>
+        <v>89.43000000000001</v>
       </c>
       <c r="AA10">
-        <v>55.17</v>
+        <v>43.58</v>
       </c>
       <c r="AB10">
-        <v>9.15</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="AC10">
-        <v>65.33</v>
+        <v>50</v>
       </c>
       <c r="AD10">
-        <v>6.08</v>
+        <v>9.85</v>
       </c>
       <c r="AE10">
-        <v>85.06999999999999</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AF10">
-        <v>-16.25</v>
+        <v>34.78</v>
       </c>
       <c r="AG10">
-        <v>6.67</v>
+        <v>12.2</v>
       </c>
       <c r="AH10" t="s">
         <v>58</v>
       </c>
       <c r="AI10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="AJ10" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AK10">
-        <v>31.44764192993779</v>
+        <v>10.39039526421124</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1719,40 +1716,40 @@
         <v>46</v>
       </c>
       <c r="B11">
-        <v>94.54545454545455</v>
+        <v>95.95959595959596</v>
       </c>
       <c r="C11">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D11">
-        <v>152.34</v>
+        <v>31.61</v>
       </c>
       <c r="E11">
-        <v>2.26</v>
+        <v>3.08</v>
       </c>
       <c r="F11">
-        <v>0.5305796158694818</v>
+        <v>-0.2952414916117862</v>
       </c>
       <c r="G11">
-        <v>2.58</v>
+        <v>3.42</v>
       </c>
       <c r="H11">
-        <v>-0.1234897361407669</v>
+        <v>0.3477500111242447</v>
       </c>
       <c r="I11">
-        <v>149.4619995117187</v>
+        <v>31.23400001525879</v>
       </c>
       <c r="J11">
-        <v>150.4575004577637</v>
+        <v>31.90300016403198</v>
       </c>
       <c r="K11">
-        <v>143.4066006469727</v>
+        <v>30.01940002441406</v>
       </c>
       <c r="L11">
-        <v>106.9570499610901</v>
+        <v>21.34519996166229</v>
       </c>
       <c r="M11">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="N11">
         <v>1.04</v>
@@ -1773,55 +1770,55 @@
         <v>0</v>
       </c>
       <c r="U11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="b">
         <v>1</v>
       </c>
       <c r="X11">
-        <v>58</v>
+        <v>9.57</v>
       </c>
       <c r="Y11">
-        <v>161.07</v>
+        <v>35.2</v>
       </c>
       <c r="Z11">
-        <v>135.21</v>
+        <v>8.77</v>
       </c>
       <c r="AA11">
-        <v>5.05</v>
+        <v>2.84</v>
       </c>
       <c r="AB11">
-        <v>3.15</v>
+        <v>153.01</v>
       </c>
       <c r="AC11">
-        <v>222.22</v>
+        <v>505.56</v>
       </c>
       <c r="AD11">
-        <v>48.71</v>
+        <v>8.49</v>
       </c>
       <c r="AE11">
-        <v>248</v>
+        <v>11050</v>
       </c>
       <c r="AF11">
-        <v>82.93000000000001</v>
+        <v>-115.38</v>
       </c>
       <c r="AG11">
-        <v>-49.38</v>
+        <v>124.07</v>
       </c>
       <c r="AH11" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="AI11" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="AJ11" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="AK11">
-        <v>30.32748182503727</v>
+        <v>74.78783011491818</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -1829,49 +1826,49 @@
         <v>47</v>
       </c>
       <c r="B12">
-        <v>96.16161616161617</v>
+        <v>98.38383838383838</v>
       </c>
       <c r="C12">
-        <v>425</v>
+        <v>277</v>
       </c>
       <c r="D12">
-        <v>259.24</v>
+        <v>46.37</v>
       </c>
       <c r="E12">
-        <v>1.42</v>
+        <v>3.14</v>
       </c>
       <c r="F12">
-        <v>-0.6025226146314466</v>
+        <v>-0.2225133822411409</v>
       </c>
       <c r="G12">
-        <v>1.93</v>
+        <v>2.9</v>
       </c>
       <c r="H12">
-        <v>-0.9002800118649513</v>
+        <v>-0.4508683109528836</v>
       </c>
       <c r="I12">
-        <v>256.4820007324219</v>
+        <v>45.54199905395508</v>
       </c>
       <c r="J12">
-        <v>246.85</v>
+        <v>45.24999980926513</v>
       </c>
       <c r="K12">
-        <v>232.9982000732422</v>
+        <v>43.09439979553223</v>
       </c>
       <c r="L12">
-        <v>196.3687998199463</v>
+        <v>34.17614988327026</v>
       </c>
       <c r="M12">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N12">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="P12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -1880,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="T12">
-        <v>2.777777777777778</v>
+        <v>0</v>
       </c>
       <c r="U12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" t="b">
         <v>1</v>
@@ -1892,46 +1889,46 @@
         <v>1</v>
       </c>
       <c r="X12">
-        <v>104.9</v>
+        <v>10.58</v>
       </c>
       <c r="Y12">
-        <v>261.13</v>
+        <v>47.74</v>
       </c>
       <c r="Z12">
-        <v>33.3</v>
+        <v>4.81</v>
       </c>
       <c r="AA12">
-        <v>25.71</v>
+        <v>-392.99</v>
       </c>
       <c r="AB12">
-        <v>3.77</v>
+        <v>34.5</v>
       </c>
       <c r="AC12">
-        <v>89.86</v>
+        <v>1387.5</v>
       </c>
       <c r="AD12">
-        <v>4</v>
+        <v>12.14</v>
       </c>
       <c r="AE12">
-        <v>-21.56</v>
+        <v>60.81</v>
       </c>
       <c r="AF12">
-        <v>128.77</v>
+        <v>8.82</v>
       </c>
       <c r="AG12">
-        <v>5.8</v>
+        <v>750</v>
       </c>
       <c r="AH12" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="AI12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AJ12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AK12">
-        <v>24.56873174614586</v>
+        <v>62.15235962850954</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -1939,46 +1936,46 @@
         <v>48</v>
       </c>
       <c r="B13">
-        <v>98.38383838383838</v>
+        <v>90.7070707070707</v>
       </c>
       <c r="C13">
-        <v>59</v>
+        <v>330</v>
       </c>
       <c r="D13">
-        <v>234.2</v>
+        <v>55.07</v>
       </c>
       <c r="E13">
-        <v>1.74</v>
+        <v>2.82</v>
       </c>
       <c r="F13">
-        <v>-0.1708646220596642</v>
+        <v>-0.6103966322179158</v>
       </c>
       <c r="G13">
-        <v>2.79</v>
+        <v>2.68</v>
       </c>
       <c r="H13">
-        <v>0.1274732760162772</v>
+        <v>-0.7887452933701298</v>
       </c>
       <c r="I13">
-        <v>234.2219970703125</v>
+        <v>54.40066604614258</v>
       </c>
       <c r="J13">
-        <v>227.1844985961914</v>
+        <v>54.40625</v>
       </c>
       <c r="K13">
-        <v>209.5193984985352</v>
+        <v>53.51766662597656</v>
       </c>
       <c r="L13">
-        <v>174.3316248703003</v>
+        <v>43.33231657981872</v>
       </c>
       <c r="M13">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="N13">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="P13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -1990,58 +1987,58 @@
         <v>0</v>
       </c>
       <c r="T13">
-        <v>0.5555555555555555</v>
+        <v>0</v>
       </c>
       <c r="U13" t="b">
         <v>0</v>
       </c>
       <c r="V13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W13" t="b">
         <v>1</v>
       </c>
       <c r="X13">
-        <v>82.06999999999999</v>
+        <v>19.74</v>
       </c>
       <c r="Y13">
-        <v>244.25</v>
+        <v>57.5</v>
       </c>
       <c r="Z13">
-        <v>234.47</v>
+        <v>8.15</v>
       </c>
       <c r="AA13">
-        <v>35.3</v>
+        <v>106.56</v>
       </c>
       <c r="AB13">
-        <v>3.09</v>
+        <v>23.7</v>
       </c>
       <c r="AC13">
-        <v>102.33</v>
+        <v>1875.23</v>
       </c>
       <c r="AD13">
-        <v>5.51</v>
+        <v>16.81</v>
       </c>
       <c r="AE13">
-        <v>-33.08</v>
+        <v>151.12</v>
       </c>
       <c r="AF13">
-        <v>1757.14</v>
+        <v>1391.86</v>
       </c>
       <c r="AG13">
-        <v>-83.72</v>
+        <v>-160.89</v>
       </c>
       <c r="AH13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="AI13" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="AJ13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AK13">
-        <v>22.99922568202899</v>
+        <v>59.53206028500831</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2049,46 +2046,46 @@
         <v>49</v>
       </c>
       <c r="B14">
-        <v>90.7070707070707</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="C14">
-        <v>36</v>
+        <v>97</v>
       </c>
       <c r="D14">
-        <v>47.23</v>
+        <v>18.58</v>
       </c>
       <c r="E14">
-        <v>1.66</v>
+        <v>3.79</v>
       </c>
       <c r="F14">
-        <v>-0.2787791202026099</v>
+        <v>0.5653744692741822</v>
       </c>
       <c r="G14">
-        <v>2.09</v>
+        <v>3.72</v>
       </c>
       <c r="H14">
-        <v>-0.7090700978405369</v>
+        <v>0.8084913507841268</v>
       </c>
       <c r="I14">
-        <v>47.72760009765625</v>
+        <v>18.87599983215332</v>
       </c>
       <c r="J14">
-        <v>48.72740020751953</v>
+        <v>18.44549999237061</v>
       </c>
       <c r="K14">
-        <v>43.84900016784668</v>
+        <v>17.74980001449585</v>
       </c>
       <c r="L14">
-        <v>34.09528991699219</v>
+        <v>15.29494997501373</v>
       </c>
       <c r="M14">
-        <v>0.98</v>
+        <v>1.02</v>
       </c>
       <c r="N14">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="P14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2100,58 +2097,58 @@
         <v>0</v>
       </c>
       <c r="T14">
-        <v>1.111111111111111</v>
+        <v>0</v>
       </c>
       <c r="U14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>18.14</v>
+        <v>6.44</v>
       </c>
       <c r="Y14">
-        <v>51.67</v>
+        <v>20.36</v>
       </c>
       <c r="Z14">
-        <v>48.85</v>
+        <v>3.48</v>
       </c>
       <c r="AA14">
-        <v>86</v>
+        <v>-211.11</v>
       </c>
       <c r="AB14">
-        <v>1.52</v>
+        <v>30.15</v>
       </c>
       <c r="AC14">
-        <v>58.82</v>
+        <v>135.38</v>
       </c>
       <c r="AD14">
-        <v>15.18</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AE14">
-        <v>18.12</v>
+        <v>109.79</v>
       </c>
       <c r="AF14">
-        <v>21.21</v>
+        <v>-128.16</v>
       </c>
       <c r="AG14">
-        <v>10.92</v>
+        <v>-58.46</v>
       </c>
       <c r="AH14" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="AI14" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="AJ14" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="AK14">
-        <v>13.7396829365093</v>
+        <v>37.6266071739815</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2159,43 +2156,43 @@
         <v>50</v>
       </c>
       <c r="B15">
-        <v>94.94949494949495</v>
+        <v>99.19191919191918</v>
       </c>
       <c r="C15">
-        <v>172</v>
+        <v>307</v>
       </c>
       <c r="D15">
-        <v>98.92</v>
+        <v>31.75</v>
       </c>
       <c r="E15">
-        <v>3.11</v>
+        <v>2.29</v>
       </c>
       <c r="F15">
-        <v>1.677171158638279</v>
+        <v>-1.252828264991948</v>
       </c>
       <c r="G15">
-        <v>3.68</v>
+        <v>2.75</v>
       </c>
       <c r="H15">
-        <v>1.191078422777084</v>
+        <v>-0.6812389807828243</v>
       </c>
       <c r="I15">
-        <v>99.96600036621093</v>
+        <v>31.89800033569336</v>
       </c>
       <c r="J15">
-        <v>93.73550033569336</v>
+        <v>32.89099988937378</v>
       </c>
       <c r="K15">
-        <v>89.07339981079102</v>
+        <v>31.18559986114502</v>
       </c>
       <c r="L15">
-        <v>64.61274993896484</v>
+        <v>22.96779998779297</v>
       </c>
       <c r="M15">
-        <v>1.07</v>
+        <v>0.97</v>
       </c>
       <c r="N15">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -2204,174 +2201,64 @@
         <v>0</v>
       </c>
       <c r="R15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T15">
-        <v>5.555555555555555</v>
+        <v>0</v>
       </c>
       <c r="U15" t="b">
         <v>0</v>
       </c>
       <c r="V15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W15" t="b">
         <v>1</v>
       </c>
       <c r="X15">
-        <v>28.47</v>
+        <v>5.5</v>
       </c>
       <c r="Y15">
-        <v>109.09</v>
+        <v>35.27</v>
       </c>
       <c r="Z15">
-        <v>7.07</v>
+        <v>6.13</v>
       </c>
       <c r="AA15">
-        <v>0.7</v>
+        <v>-136.86</v>
       </c>
       <c r="AB15">
-        <v>457.63</v>
+        <v>19.69</v>
       </c>
       <c r="AC15">
-        <v>360.71</v>
+        <v>99.61</v>
       </c>
       <c r="AD15">
-        <v>2.87</v>
+        <v>2.47</v>
       </c>
       <c r="AE15">
-        <v>317.14</v>
+        <v>-118.75</v>
       </c>
       <c r="AF15">
-        <v>-59.3</v>
+        <v>-23.81</v>
       </c>
       <c r="AG15">
-        <v>253.57</v>
+        <v>102.76</v>
       </c>
       <c r="AH15" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="AI15" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="AJ15" t="s">
         <v>77</v>
       </c>
       <c r="AK15">
-        <v>80.13971215893459</v>
-      </c>
-    </row>
-    <row r="16" spans="1:37">
-      <c r="A16" t="s">
-        <v>51</v>
-      </c>
-      <c r="B16">
-        <v>90.50505050505051</v>
-      </c>
-      <c r="C16">
-        <v>446</v>
-      </c>
-      <c r="D16">
-        <v>119.61</v>
-      </c>
-      <c r="E16">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="F16">
-        <v>-1.25000960348912</v>
-      </c>
-      <c r="G16">
-        <v>1.8</v>
-      </c>
-      <c r="H16">
-        <v>-1.055638067009788</v>
-      </c>
-      <c r="I16">
-        <v>119.1099990844727</v>
-      </c>
-      <c r="J16">
-        <v>115.5965003967285</v>
-      </c>
-      <c r="K16">
-        <v>103.4454002380371</v>
-      </c>
-      <c r="L16">
-        <v>83.90685022354126</v>
-      </c>
-      <c r="M16">
-        <v>1.03</v>
-      </c>
-      <c r="N16">
-        <v>1.15</v>
-      </c>
-      <c r="P16">
-        <v>15</v>
-      </c>
-      <c r="Q16">
-        <v>5</v>
-      </c>
-      <c r="R16">
-        <v>1</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16">
-        <v>15</v>
-      </c>
-      <c r="U16" t="b">
-        <v>1</v>
-      </c>
-      <c r="V16" t="b">
-        <v>1</v>
-      </c>
-      <c r="W16" t="b">
-        <v>1</v>
-      </c>
-      <c r="X16">
-        <v>43.9</v>
-      </c>
-      <c r="Y16">
-        <v>121.75</v>
-      </c>
-      <c r="Z16">
-        <v>9.619999999999999</v>
-      </c>
-      <c r="AA16">
-        <v>565</v>
-      </c>
-      <c r="AB16">
-        <v>1312.5</v>
-      </c>
-      <c r="AC16">
-        <v>48.39</v>
-      </c>
-      <c r="AD16">
-        <v>3.71</v>
-      </c>
-      <c r="AE16">
-        <v>53.33</v>
-      </c>
-      <c r="AF16">
-        <v>400</v>
-      </c>
-      <c r="AG16">
-        <v>-80.65000000000001</v>
-      </c>
-      <c r="AH16" t="s">
-        <v>52</v>
-      </c>
-      <c r="AI16" t="s">
-        <v>63</v>
-      </c>
-      <c r="AJ16" t="s">
-        <v>78</v>
-      </c>
-      <c r="AK16">
-        <v>76.11578259277927</v>
+        <v>28.4210052117461</v>
       </c>
     </row>
   </sheetData>
